--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>AGORA Data, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=79de8f5046781d37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Data Architect (172951)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783168b15946ba04</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,69 +2341,69 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41506061e08a6c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=783168b15946ba04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f05c8dd67fcf30</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Verato</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Full Stack Software Engineer, AI Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Talend</t>
+          <t>AWS, GCP, Vertex AI, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791202dbdbb21c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=624a180836a37e71</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, AI Integration</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624a180836a37e71</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Cloud Solutions Architect (In-Person)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=feebd610eac70e67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (In-Person)</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feebd610eac70e67</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,102 +3856,102 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Founding Product Designer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OrangeAI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Naples, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Chronosphere Sales Specialist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior QA Engineer / SDET</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>New Classrooms Innovation Partners Inc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, pytest, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+          <t>https://www.indeed.com/viewjob?jk=456b9250ee924554</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Scala, Power BI, Tableau, Git, Python, SQL, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Research Fellow - Artificial Intelligence/Machine Learning</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Amherst, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Dask, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae29c34d0c2ccf3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Azure, Hive, Scala, Power BI, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,147 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>AI Application Developer III -Houston, TX</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,7 +923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=23fd00a4507ab066</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b858fbab54a4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data and AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Refresco</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af7139898138970</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Progress Residential</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Data and AI Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Refresco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=2af7139898138970</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Progress Residential</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AGORA Data, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79de8f5046781d37</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect (172951)</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Data Architect (172951)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783168b15946ba04</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (In-Person)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feebd610eac70e67</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Cloud Solutions Architect (In-Person)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>New York Cancer and Blood Specialists</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridge, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=feebd610eac70e67</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Founding Product Designer</t>
+          <t>Sr Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OrangeAI</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Naples, FL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d564e3ba391555e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Chronosphere Sales Specialist</t>
+          <t>Sr Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdaf375e812bc96</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Founding Product Designer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>OrangeAI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Naples, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Chronosphere Sales Specialist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior QA Engineer / SDET</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>New Classrooms Innovation Partners Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, pytest, Git, CloudWatch</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456b9250ee924554</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Senior QA Engineer / SDET</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New Classrooms Innovation Partners Inc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, pytest, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=456b9250ee924554</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,15 +5001,120 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GE HealthCare</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AWS, Azure, Hive, Scala, Power BI, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Catalyst Brands</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fd00a4507ab066</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b858fbab54a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data and AI Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Refresco</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af7139898138970</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Progress Residential</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect (172951)</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, AI Integration</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624a180836a37e71</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (In-Person)</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New York Cancer and Blood Specialists</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ridge, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feebd610eac70e67</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer (GCP)</t>
+          <t>Chronosphere Sales Specialist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d564e3ba391555e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer (GCP)</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdaf375e812bc96</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Founding Product Designer</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OrangeAI</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Naples, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,647 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Chronosphere Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer / SDET</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>New Classrooms Innovation Partners Inc</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, pytest, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=456b9250ee924554</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Notification Platform</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Marathon TS</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>GE HealthCare</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Hive, Scala, Power BI, Tableau, Git, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,15 +2683,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4170,321 +4170,6 @@
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Chronosphere Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb135d3bc1e4d5f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>People Data Analytics Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SNS, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7f2c525086c9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d3903be92908c75d</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02450496a854e90</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7f2c525086c9e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MID-LEVEL DATA ENGINEER-Python, AWS, Spark (Hybrid)</t>
+          <t>People Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261c84436f020c86</t>
+          <t>https://www.indeed.com/viewjob?jk=b02450496a854e90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
+          <t>AI Technical Architect - Onsite</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>NTT Global Data Centers Americas, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, API Gateway, ECS</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7327c0bf569365fa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>MID-LEVEL DATA ENGINEER-Python, AWS, Spark (Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=261c84436f020c86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=81fe8958cd4a14a2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=5335254820a6db07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,137 +2036,137 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=587fb03845771fd7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
@@ -2258,55 +2258,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,46 +2827,46 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=05932e2bdc0b6ca7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,137 +3191,137 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=4a139e85dc1c56b0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Kubernetes Automation Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c39b3c6df926e3a2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,15 +4161,400 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Java/ Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Marathon TS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Altumint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fed653aec24910be</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=23fd00a4507ab066</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b858fbab54a4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fb03845771fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Data Architect (172951)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,104 +2201,104 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=587fb03845771fd7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Full Stack Software Engineer, AI Integration</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Vertex AI, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=624a180836a37e71</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05932e2bdc0b6ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a139e85dc1c56b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=05932e2bdc0b6ca7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a139e85dc1c56b0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kubernetes Automation Engineer</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39b3c6df926e3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>Azure, HBase, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c98e70b4f08875</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Kubernetes Automation Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=c39b3c6df926e3a2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Sr Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d564e3ba391555e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Sr Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdaf375e812bc96</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Founding Product Designer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>OrangeAI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Naples, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,262 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>People Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>US Pharmacopeial Convention</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7f2c525086c9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02450496a854e90</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7f2c525086c9e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Technical Architect - Onsite</t>
+          <t>People Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT Global Data Centers Americas, Inc.</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7327c0bf569365fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b02450496a854e90</t>
         </is>
       </c>
     </row>
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5335254820a6db07</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Altumint</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed653aec24910be</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fd00a4507ab066</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b858fbab54a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,46 +1147,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,277 +2106,277 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect (172951)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253a8faafcf61b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fb03845771fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Backend Engineer - Mobile Team</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb4d8c9f3f81a5e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, AI Integration</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,42 +2866,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624a180836a37e71</t>
+          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05932e2bdc0b6ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a139e85dc1c56b0</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, HBase, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c98e70b4f08875</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kubernetes Automation Engineer</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39b3c6df926e3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer (GCP)</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,542 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d564e3ba391555e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Sr Platform Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>O'Reilly Auto Parts</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdaf375e812bc96</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Founding Product Designer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>OrangeAI</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Naples, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de8acdb2ac2aff1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Notification Platform</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Marathon TS</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,165 +713,165 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Cloud Operations Associate (GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>Junior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Gointellects Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,46 +1147,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,172 +1231,172 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Senior DevOps / Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Zingtree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,112 +1956,112 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Backend Engineer - Mobile Team</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb4d8c9f3f81a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,137 +2421,137 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer - Mobile Team</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Fingerprint</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb4d8c9f3f81a5e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,164 +3121,164 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,137 +3471,137 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Soft Engineering- Portals - QA Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=28df02e9ebcc6a84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68aa85a5e2fb315</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,15 +4266,365 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Junior Automation Engineer (Cloud)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Notification Platform</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,42 +678,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, API Gateway, ECS</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Cloud Operations Associate (GCP)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Operations Associate (GCP)</t>
+          <t>Junior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Kubernetes Engineer</t>
+          <t>DHCF Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior DevOps / Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Zingtree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Reliability Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zingtree</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Engineer - Mobile Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fingerprint</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, BigQuery, Scala, Snowflake, DynamoDB, dbt, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb4d8c9f3f81a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Soft Engineering- Portals - QA Engineer II</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28df02e9ebcc6a84</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4485,146 +4485,6 @@
         </is>
       </c>
       <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>CapTech Consulting</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
+          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Operations Associate (GCP)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Kubernetes Engineer</t>
+          <t>Cloud Operations Associate (GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHCF Azure Data Solutions Architect</t>
+          <t>Junior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
+          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Solutions Architect</t>
+          <t>DHCF Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gointellects Inc.</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gointellects Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
+          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Associate Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,104 +976,104 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Reliability Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zingtree</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9a604036ab5e2b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior DevOps / Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zingtree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=794fd3442926e801</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Junior Generative AI Application Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=29931ba9e2678a00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,129 +3786,129 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,24 +3986,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,15 +4476,120 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineer I or II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SNS, IAM</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3903be92908c75d</t>
+          <t>https://www.indeed.com/viewjob?jk=432940e5c429b71c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I or II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>US Pharmacopeial Convention</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
+          <t>https://www.indeed.com/viewjob?jk=94efcb73c0d62620</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>People Data Analytics Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SNS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7f2c525086c9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d3903be92908c75d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>People Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>US Pharmacopeial Convention</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Data Lake Storage, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b02450496a854e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,137 +986,137 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer- Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer- Full Stack</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94f6b732ffad456</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9a604036ab5e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Reliability Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zingtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Kafka, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,129 +1406,129 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fd3442926e801</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,147 +1781,147 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,244 +2026,244 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Full Stack Engineer (Typescript/React)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,129 +2491,129 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,94 +3401,94 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Engineer III, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Tableau, Splunk, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,42 +3496,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AWS Serverless Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29931ba9e2678a00</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Rocket 55</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,54 +3821,54 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3877,11 +3877,11 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Senior Software Engineer - Notification Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,435 +4161,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Dun &amp; Bradstreet</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Notification Platform</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Trust</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>

--- a/results/job_matches_2026-05-08.xlsx
+++ b/results/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>GCP API Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=653da5ce67465bb9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=2457ccbf333a6c71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,164 +1441,164 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Derivatives Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (Sweep)</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Derivatives Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, RDS, Databricks, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,312 +2036,312 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5fb021bee91d230</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=e256491381390022</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=31b534428b0f5a04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c509b3fc36b7555a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c86e1f482263817</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=dedcabb346dbfd79</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb6c8b91428f3de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a129185acbd0492</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Typescript/React)</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c646c37ffe153e</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Software Engineer (Sweep)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=ede73743d3508e4e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b691898c1cbce1f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Vanco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,137 +2946,137 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, BigQuery, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=4055b22190d144e0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,137 +3401,137 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer III, Advanced Research (Remote)</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Systems Data Engineer, Financial Transactions and Automation - GeForce NOW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=d44146696368c097</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+          <t>Platform Engineer - Databricks</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+          <t>https://www.indeed.com/viewjob?jk=07c7ca9178811a63</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3429f80acb97235f</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,137 +3961,137 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Notification Platform</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Junior Backend Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,75 +4101,1265 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Trust</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Consertus</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Engineer / Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GreenStone Farm Credit Services</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>East Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Luminate</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Google Cloud Solution Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Google Cloud Solution Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Azure Databricks Senior Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SRE/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer - SRE</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Engineer III, Advanced Research (Remote)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac40b26524188b31</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Factored</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, pytest</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Busigence Technologies</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Engineer, (L2) CDP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2df0d1cb02cd182</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>GT Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Engineer (Analytics)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Rocket 55</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Junior Automation Engineer (Cloud)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Marketing Analytics (R-19206)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Dun &amp; Bradstreet</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Redshift, GCP, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=522b6aa7f1ff3be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Junior Automation Engineer (Cloud)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Notification Platform</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9064827704bc8b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ApolloMD</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Junior Backend Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Senior Software Engineer, Data Trust</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>SoFi</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061e72325e6d3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Trust</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Seattle, WA, US USA</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D141" t="n">
         <v>10.4</v>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c04679e26ef882f0</t>
         </is>
